--- a/products/small-business-bookkeeping-tracker.xlsx
+++ b/products/small-business-bookkeeping-tracker.xlsx
@@ -15,6 +15,11 @@
     <sheet name="Dashboard" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Dashboard!$A$1:$M$50</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Expenses!$A$1:$D$40</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Income!$A$1:$G$40</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Products!$A$1:$D$28</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Start Here'!$A$1:$H$27</definedName>
     <definedName function="false" hidden="false" name="ProductList" vbProcedure="false">Products!$A$6:$A$25</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="88">
   <si>
     <t xml:space="preserve">Small Business Bookkeeping Tracker</t>
   </si>
@@ -203,7 +208,7 @@
     <t xml:space="preserve">Month by month</t>
   </si>
   <si>
-    <t xml:space="preserve">By platform</t>
+    <t xml:space="preserve">By platform — where fees eat you</t>
   </si>
   <si>
     <t xml:space="preserve">By product</t>
@@ -224,6 +229,12 @@
     <t xml:space="preserve">Net revenue</t>
   </si>
   <si>
+    <t xml:space="preserve">Fees paid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fee %</t>
+  </si>
+  <si>
     <t xml:space="preserve">Product</t>
   </si>
   <si>
@@ -267,6 +278,24 @@
   </si>
   <si>
     <t xml:space="preserve">December</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarter by quarter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4</t>
   </si>
 </sst>
 </file>
@@ -544,7 +573,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -662,6 +691,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1068,11 +1101,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="23091836"/>
-        <c:axId val="18132272"/>
+        <c:axId val="5217750"/>
+        <c:axId val="3674325"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="23091836"/>
+        <c:axId val="5217750"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1104,7 +1137,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18132272"/>
+        <c:crossAx val="3674325"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1112,7 +1145,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18132272"/>
+        <c:axId val="3674325"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1154,7 +1187,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23091836"/>
+        <c:crossAx val="5217750"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1212,14 +1245,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>692280</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>94320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1227,7 +1260,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="355680" y="5133960"/>
+        <a:off x="355680" y="6524640"/>
         <a:ext cx="5759640" cy="2951640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1420,7 +1453,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF6D5FC7"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -1582,8 +1615,8 @@
     <mergeCell ref="C18:H18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1595,7 +1628,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF3F3D77"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -1749,8 +1782,8 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1762,7 +1795,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF3F3D77"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:G305"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -5484,8 +5517,8 @@
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -5497,7 +5530,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF3F3D77"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:D305"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -7371,8 +7404,8 @@
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -7384,21 +7417,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF6D5FC7"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7415,6 +7449,8 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -7430,6 +7466,8 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -7486,7 +7524,7 @@
       <c r="G10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="L10" s="5" t="s">
         <v>59</v>
       </c>
     </row>
@@ -7512,10 +7550,16 @@
       <c r="H11" s="11" t="s">
         <v>64</v>
       </c>
+      <c r="I11" s="11" t="s">
+        <v>65</v>
+      </c>
       <c r="J11" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11" s="11" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7524,7 +7568,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A12,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A12+1,1))</f>
@@ -7545,12 +7589,20 @@
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$C$6:$C$305,"Gumroad",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>22.68</v>
       </c>
-      <c r="J12" s="27" t="str">
+      <c r="I12" s="28" t="n">
+        <f aca="false">SUMIFS(Income!$E$6:$E$305,Income!$C$6:$C$305,"Gumroad",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
+        <v>3.32</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <f aca="false">IF(SUMIFS(Income!$D$6:$D$305,Income!$C$6:$C$305,"Gumroad",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))=0,"",$I12/SUMIFS(Income!$D$6:$D$305,Income!$C$6:$C$305,"Gumroad",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v>0.127692307692308</v>
+      </c>
+      <c r="L12" s="27" t="str">
         <f aca="false">IF(Products!A6="","",Products!A6)</f>
         <v>Budget Template</v>
       </c>
-      <c r="K12" s="28" t="n">
-        <f aca="false">IF($J12="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J12,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M12" s="28" t="n">
+        <f aca="false">IF($L12="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L12,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v>19.73</v>
       </c>
     </row>
@@ -7559,7 +7611,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A13,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A13+1,1))</f>
@@ -7580,12 +7632,20 @@
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$C$6:$C$305,"Etsy",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>9.28</v>
       </c>
-      <c r="J13" s="27" t="str">
+      <c r="I13" s="28" t="n">
+        <f aca="false">SUMIFS(Income!$E$6:$E$305,Income!$C$6:$C$305,"Etsy",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
+        <v>2.72</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <f aca="false">IF(SUMIFS(Income!$D$6:$D$305,Income!$C$6:$C$305,"Etsy",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))=0,"",$I13/SUMIFS(Income!$D$6:$D$305,Income!$C$6:$C$305,"Etsy",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v>0.226666666666667</v>
+      </c>
+      <c r="L13" s="27" t="str">
         <f aca="false">IF(Products!A7="","",Products!A7)</f>
         <v>Invoice Template Pack</v>
       </c>
-      <c r="K13" s="28" t="n">
-        <f aca="false">IF($J13="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J13,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M13" s="28" t="n">
+        <f aca="false">IF($L13="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L13,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v>26.23</v>
       </c>
     </row>
@@ -7594,7 +7654,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C14" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A14,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A14+1,1))</f>
@@ -7609,18 +7669,26 @@
         <v>0</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H14" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$C$6:$C$305,"Shopify",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>0</v>
       </c>
-      <c r="J14" s="27" t="str">
+      <c r="I14" s="28" t="n">
+        <f aca="false">SUMIFS(Income!$E$6:$E$305,Income!$C$6:$C$305,"Shopify",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="str">
+        <f aca="false">IF(SUMIFS(Income!$D$6:$D$305,Income!$C$6:$C$305,"Shopify",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))=0,"",$I14/SUMIFS(Income!$D$6:$D$305,Income!$C$6:$C$305,"Shopify",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+      <c r="L14" s="27" t="str">
         <f aca="false">IF(Products!A8="","",Products!A8)</f>
         <v/>
       </c>
-      <c r="K14" s="28" t="str">
-        <f aca="false">IF($J14="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J14,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M14" s="28" t="str">
+        <f aca="false">IF($L14="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L14,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
@@ -7629,7 +7697,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C15" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A15,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A15+1,1))</f>
@@ -7650,12 +7718,20 @@
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$C$6:$C$305,"Direct",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>14</v>
       </c>
-      <c r="J15" s="27" t="str">
+      <c r="I15" s="28" t="n">
+        <f aca="false">SUMIFS(Income!$E$6:$E$305,Income!$C$6:$C$305,"Direct",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <f aca="false">IF(SUMIFS(Income!$D$6:$D$305,Income!$C$6:$C$305,"Direct",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))=0,"",$I15/SUMIFS(Income!$D$6:$D$305,Income!$C$6:$C$305,"Direct",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="27" t="str">
         <f aca="false">IF(Products!A9="","",Products!A9)</f>
         <v/>
       </c>
-      <c r="K15" s="28" t="str">
-        <f aca="false">IF($J15="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J15,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M15" s="28" t="str">
+        <f aca="false">IF($L15="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L15,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
@@ -7664,7 +7740,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C16" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A16,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A16+1,1))</f>
@@ -7679,18 +7755,26 @@
         <v>0</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H16" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$C$6:$C$305,"Other",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
         <v>0</v>
       </c>
-      <c r="J16" s="27" t="str">
+      <c r="I16" s="28" t="n">
+        <f aca="false">SUMIFS(Income!$E$6:$E$305,Income!$C$6:$C$305,"Other",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="30" t="str">
+        <f aca="false">IF(SUMIFS(Income!$D$6:$D$305,Income!$C$6:$C$305,"Other",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))=0,"",$I16/SUMIFS(Income!$D$6:$D$305,Income!$C$6:$C$305,"Other",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+      <c r="L16" s="27" t="str">
         <f aca="false">IF(Products!A10="","",Products!A10)</f>
         <v/>
       </c>
-      <c r="K16" s="28" t="str">
-        <f aca="false">IF($J16="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J16,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M16" s="28" t="str">
+        <f aca="false">IF($L16="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L16,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
@@ -7699,7 +7783,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C17" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A17,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A17+1,1))</f>
@@ -7713,12 +7797,12 @@
         <f aca="false">C17-D17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="27" t="str">
+      <c r="L17" s="27" t="str">
         <f aca="false">IF(Products!A11="","",Products!A11)</f>
         <v/>
       </c>
-      <c r="K17" s="28" t="str">
-        <f aca="false">IF($J17="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J17,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M17" s="28" t="str">
+        <f aca="false">IF($L17="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L17,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
@@ -7727,7 +7811,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C18" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A18,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A18+1,1))</f>
@@ -7741,12 +7825,12 @@
         <f aca="false">C18-D18</f>
         <v>9.69</v>
       </c>
-      <c r="J18" s="27" t="str">
+      <c r="L18" s="27" t="str">
         <f aca="false">IF(Products!A12="","",Products!A12)</f>
         <v/>
       </c>
-      <c r="K18" s="28" t="str">
-        <f aca="false">IF($J18="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J18,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M18" s="28" t="str">
+        <f aca="false">IF($L18="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L18,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
@@ -7755,7 +7839,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C19" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A19,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A19+1,1))</f>
@@ -7769,12 +7853,12 @@
         <f aca="false">C19-D19</f>
         <v>-1.72</v>
       </c>
-      <c r="J19" s="27" t="str">
+      <c r="L19" s="27" t="str">
         <f aca="false">IF(Products!A13="","",Products!A13)</f>
         <v/>
       </c>
-      <c r="K19" s="28" t="str">
-        <f aca="false">IF($J19="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J19,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M19" s="28" t="str">
+        <f aca="false">IF($L19="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L19,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
@@ -7783,7 +7867,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C20" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A20,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A20+1,1))</f>
@@ -7797,12 +7881,12 @@
         <f aca="false">C20-D20</f>
         <v>0</v>
       </c>
-      <c r="J20" s="30" t="str">
+      <c r="L20" s="31" t="str">
         <f aca="false">IF(Products!A14="","",Products!A14)</f>
         <v/>
       </c>
-      <c r="K20" s="31" t="str">
-        <f aca="false">IF($J20="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J20,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M20" s="32" t="str">
+        <f aca="false">IF($L20="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L20,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
@@ -7811,7 +7895,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C21" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A21,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A21+1,1))</f>
@@ -7825,12 +7909,12 @@
         <f aca="false">C21-D21</f>
         <v>0</v>
       </c>
-      <c r="J21" s="30" t="str">
+      <c r="L21" s="31" t="str">
         <f aca="false">IF(Products!A15="","",Products!A15)</f>
         <v/>
       </c>
-      <c r="K21" s="31" t="str">
-        <f aca="false">IF($J21="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J21,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M21" s="32" t="str">
+        <f aca="false">IF($L21="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L21,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
@@ -7839,7 +7923,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C22" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A22,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A22+1,1))</f>
@@ -7853,12 +7937,12 @@
         <f aca="false">C22-D22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="30" t="str">
+      <c r="L22" s="31" t="str">
         <f aca="false">IF(Products!A16="","",Products!A16)</f>
         <v/>
       </c>
-      <c r="K22" s="31" t="str">
-        <f aca="false">IF($J22="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J22,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M22" s="32" t="str">
+        <f aca="false">IF($L22="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L22,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
@@ -7867,7 +7951,7 @@
         <v>12</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C23" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A23,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A23+1,1))</f>
@@ -7881,99 +7965,189 @@
         <f aca="false">C23-D23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="30" t="str">
+      <c r="L23" s="31" t="str">
         <f aca="false">IF(Products!A17="","",Products!A17)</f>
         <v/>
       </c>
-      <c r="K23" s="31" t="str">
-        <f aca="false">IF($J23="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J23,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M23" s="32" t="str">
+        <f aca="false">IF($L23="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L23,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J24" s="30" t="str">
+      <c r="L24" s="31" t="str">
         <f aca="false">IF(Products!A18="","",Products!A18)</f>
         <v/>
       </c>
-      <c r="K24" s="31" t="str">
-        <f aca="false">IF($J24="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J24,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M24" s="32" t="str">
+        <f aca="false">IF($L24="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L24,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J25" s="30" t="str">
+      <c r="B25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="L25" s="31" t="str">
         <f aca="false">IF(Products!A19="","",Products!A19)</f>
         <v/>
       </c>
-      <c r="K25" s="31" t="str">
-        <f aca="false">IF($J25="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J25,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J26" s="30" t="str">
+      <c r="M25" s="32" t="str">
+        <f aca="false">IF($L25="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L25,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L26" s="31" t="str">
         <f aca="false">IF(Products!A20="","",Products!A20)</f>
         <v/>
       </c>
-      <c r="K26" s="31" t="str">
-        <f aca="false">IF($J26="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J26,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M26" s="32" t="str">
+        <f aca="false">IF($L26="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L26,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J27" s="30" t="str">
+      <c r="A27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="28" t="n">
+        <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A27-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A27+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="28" t="n">
+        <f aca="false">SUMIFS(Expenses!$D$6:$D$305,Expenses!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A27-2,1),Expenses!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A27+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="29" t="n">
+        <f aca="false">C27-D27</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="31" t="str">
         <f aca="false">IF(Products!A21="","",Products!A21)</f>
         <v/>
       </c>
-      <c r="K27" s="31" t="str">
-        <f aca="false">IF($J27="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J27,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M27" s="32" t="str">
+        <f aca="false">IF($L27="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L27,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J28" s="30" t="str">
+      <c r="A28" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="28" t="n">
+        <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A28-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A28+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="28" t="n">
+        <f aca="false">SUMIFS(Expenses!$D$6:$D$305,Expenses!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A28-2,1),Expenses!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A28+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="29" t="n">
+        <f aca="false">C28-D28</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="31" t="str">
         <f aca="false">IF(Products!A22="","",Products!A22)</f>
         <v/>
       </c>
-      <c r="K28" s="31" t="str">
-        <f aca="false">IF($J28="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J28,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M28" s="32" t="str">
+        <f aca="false">IF($L28="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L28,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J29" s="30" t="str">
+      <c r="A29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="28" t="n">
+        <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A29-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A29+1,1))</f>
+        <v>45.96</v>
+      </c>
+      <c r="D29" s="28" t="n">
+        <f aca="false">SUMIFS(Expenses!$D$6:$D$305,Expenses!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A29-2,1),Expenses!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A29+1,1))</f>
+        <v>37.99</v>
+      </c>
+      <c r="E29" s="29" t="n">
+        <f aca="false">C29-D29</f>
+        <v>7.97</v>
+      </c>
+      <c r="L29" s="31" t="str">
         <f aca="false">IF(Products!A23="","",Products!A23)</f>
         <v/>
       </c>
-      <c r="K29" s="31" t="str">
-        <f aca="false">IF($J29="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J29,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M29" s="32" t="str">
+        <f aca="false">IF($L29="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L29,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J30" s="30" t="str">
+      <c r="A30" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="28" t="n">
+        <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A30-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A30+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="28" t="n">
+        <f aca="false">SUMIFS(Expenses!$D$6:$D$305,Expenses!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A30-2,1),Expenses!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A30+1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="29" t="n">
+        <f aca="false">C30-D30</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="31" t="str">
         <f aca="false">IF(Products!A24="","",Products!A24)</f>
         <v/>
       </c>
-      <c r="K30" s="31" t="str">
-        <f aca="false">IF($J30="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J30,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M30" s="32" t="str">
+        <f aca="false">IF($L30="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L30,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J31" s="30" t="str">
+      <c r="L31" s="31" t="str">
         <f aca="false">IF(Products!A25="","",Products!A25)</f>
         <v/>
       </c>
-      <c r="K31" s="31" t="str">
-        <f aca="false">IF($J31="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$J31,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
+      <c r="M31" s="32" t="str">
+        <f aca="false">IF($L31="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L31,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="G6:H6"/>
@@ -7984,8 +8158,8 @@
     <mergeCell ref="J7:K7"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/products/small-business-bookkeeping-tracker.xlsx
+++ b/products/small-business-bookkeeping-tracker.xlsx
@@ -19,7 +19,7 @@
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Expenses!$A$1:$D$40</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Income!$A$1:$G$40</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Products!$A$1:$D$28</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Start Here'!$A$1:$H$27</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Start Here'!$A$1:$H$28</definedName>
     <definedName function="false" hidden="false" name="ProductList" vbProcedure="false">Products!$A$6:$A$25</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="89">
   <si>
     <t xml:space="preserve">Small Business Bookkeeping Tracker</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t xml:space="preserve">This is a bookkeeping aid, not tax or accounting advice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulas are protected so you can't break anything by accident — every cell meant for typing is unlocked. To change anything else: Review → Unprotect Sheet (no password).</t>
   </si>
   <si>
     <t xml:space="preserve">Products</t>
@@ -622,41 +625,41 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
@@ -1101,11 +1104,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5217750"/>
-        <c:axId val="3674325"/>
+        <c:axId val="68133661"/>
+        <c:axId val="75531703"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5217750"/>
+        <c:axId val="68133661"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1137,7 +1140,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3674325"/>
+        <c:crossAx val="75531703"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1145,7 +1148,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3674325"/>
+        <c:axId val="75531703"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1187,7 +1190,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5217750"/>
+        <c:crossAx val="68133661"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1452,10 +1455,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF6D5FC7"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1604,7 +1606,13 @@
         <v>17</v>
       </c>
     </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
   <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -1627,7 +1635,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF3F3D77"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:D25"/>
@@ -1641,7 +1648,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1649,7 +1656,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1657,29 +1664,29 @@
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="13" t="n">
         <v>12</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>14</v>
@@ -1777,6 +1784,7 @@
       <c r="C25" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -1794,7 +1802,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF3F3D77"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:G305"/>
@@ -1809,7 +1816,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1820,7 +1827,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1831,30 +1838,30 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1862,10 +1869,10 @@
         <v>46217</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="16" t="n">
         <v>12</v>
@@ -1878,7 +1885,7 @@
         <v>10.45</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1886,10 +1893,10 @@
         <v>46231</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="20" t="n">
         <v>14</v>
@@ -1908,10 +1915,10 @@
         <v>46236</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" s="16" t="n">
         <v>12</v>
@@ -1924,7 +1931,7 @@
         <v>9.28</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1932,10 +1939,10 @@
         <v>46243</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="20" t="n">
         <v>14</v>
@@ -1946,7 +1953,7 @@
         <v>14</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5502,6 +5509,7 @@
       <c r="G305" s="19"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -5529,7 +5537,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF3F3D77"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:D305"/>
@@ -5543,7 +5550,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5551,7 +5558,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5559,21 +5566,21 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5581,10 +5588,10 @@
         <v>46213</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="16" t="n">
         <v>12.99</v>
@@ -5595,10 +5602,10 @@
         <v>46239</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="20" t="n">
         <v>25</v>
@@ -7393,6 +7400,7 @@
       <c r="D305" s="20"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -7416,7 +7424,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FF6D5FC7"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:M31"/>
@@ -7437,7 +7444,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7454,7 +7461,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7471,7 +7478,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>2026</v>
@@ -7479,19 +7486,19 @@
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="21"/>
       <c r="G6" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H6" s="21"/>
       <c r="J6" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K6" s="21"/>
     </row>
@@ -7519,48 +7526,48 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I11" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="M11" s="11" t="s">
         <v>65</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7568,7 +7575,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A12,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A12+1,1))</f>
@@ -7583,7 +7590,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H12" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$C$6:$C$305,"Gumroad",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
@@ -7611,7 +7618,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A13,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A13+1,1))</f>
@@ -7626,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H13" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$C$6:$C$305,"Etsy",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
@@ -7654,7 +7661,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A14,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A14+1,1))</f>
@@ -7669,7 +7676,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H14" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$C$6:$C$305,"Shopify",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
@@ -7697,7 +7704,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A15,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A15+1,1))</f>
@@ -7712,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H15" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$C$6:$C$305,"Direct",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
@@ -7740,7 +7747,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C16" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A16,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A16+1,1))</f>
@@ -7755,7 +7762,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H16" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$C$6:$C$305,"Other",Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))</f>
@@ -7783,7 +7790,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C17" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A17,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A17+1,1))</f>
@@ -7811,7 +7818,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A18,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A18+1,1))</f>
@@ -7839,7 +7846,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A19,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A19+1,1))</f>
@@ -7867,7 +7874,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C20" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A20,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A20+1,1))</f>
@@ -7895,7 +7902,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A21,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A21+1,1))</f>
@@ -7923,7 +7930,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A22,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A22+1,1))</f>
@@ -7951,7 +7958,7 @@
         <v>12</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A23,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A23+1,1))</f>
@@ -7986,7 +7993,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L25" s="31" t="str">
         <f aca="false">IF(Products!A19="","",Products!A19)</f>
@@ -7999,19 +8006,19 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L26" s="31" t="str">
         <f aca="false">IF(Products!A20="","",Products!A20)</f>
@@ -8027,7 +8034,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C27" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A27-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A27+1,1))</f>
@@ -8055,7 +8062,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C28" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A28-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A28+1,1))</f>
@@ -8083,7 +8090,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C29" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A29-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A29+1,1))</f>
@@ -8111,7 +8118,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30" s="28" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A30-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A30+1,1))</f>
@@ -8145,6 +8152,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
   <mergeCells count="10">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>

--- a/products/small-business-bookkeeping-tracker.xlsx
+++ b/products/small-business-bookkeeping-tracker.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="90">
   <si>
     <t xml:space="preserve">Small Business Bookkeeping Tracker</t>
   </si>
@@ -268,6 +268,9 @@
     <t xml:space="preserve">July</t>
   </si>
   <si>
+    <t xml:space="preserve">INSIGHTS — written automatically from your numbers</t>
+  </si>
+  <si>
     <t xml:space="preserve">August</t>
   </si>
   <si>
@@ -313,7 +316,7 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,6 +465,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -582,7 +593,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -715,6 +726,18 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -732,6 +755,48 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF3F3D77"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9FAFC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F2937"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4F6FA"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1118,11 +1183,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="81657929"/>
-        <c:axId val="6541764"/>
+        <c:axId val="95914653"/>
+        <c:axId val="15096661"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81657929"/>
+        <c:axId val="95914653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1154,7 +1219,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6541764"/>
+        <c:crossAx val="15096661"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1162,7 +1227,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6541764"/>
+        <c:axId val="15096661"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1204,7 +1269,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81657929"/>
+        <c:crossAx val="95914653"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1274,7 +1339,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="281880" y="7020000"/>
+        <a:off x="281880" y="7391520"/>
         <a:ext cx="5759640" cy="2951640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1286,6 +1351,33 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExpenseLog" displayName="ExpenseLog" ref="A5:D305" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:D305"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Category"/>
+    <tableColumn id="3" name="Description"/>
+    <tableColumn id="4" name="Amount"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SalesLog" displayName="SalesLog" ref="A5:G305" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A5:G305"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Product / service"/>
+    <tableColumn id="3" name="Platform"/>
+    <tableColumn id="4" name="Gross"/>
+    <tableColumn id="5" name="Fees"/>
+    <tableColumn id="6" name="Net"/>
+    <tableColumn id="7" name="Notes"/>
+  </tableColumns>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6069,7 +6161,7 @@
       <c r="G305" s="21"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" autoFilter="false"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -6091,6 +6183,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -7960,7 +8055,7 @@
       <c r="D305" s="22"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" autoFilter="false"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -7978,6 +8073,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -8499,7 +8597,7 @@
       </c>
       <c r="N17" s="2"/>
     </row>
-    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="n">
         <v>7</v>
       </c>
@@ -8519,10 +8617,12 @@
         <v>9.69</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="G18" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
       <c r="K18" s="2"/>
       <c r="L18" s="29" t="str">
         <f aca="false">IF(Products!A12="","",Products!A12)</f>
@@ -8534,12 +8634,12 @@
       </c>
       <c r="N18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="n">
         <v>8</v>
       </c>
       <c r="B19" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C19" s="30" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A19,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A19+1,1))</f>
@@ -8554,10 +8654,13 @@
         <v>-1.72</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="G19" s="35" t="str">
+        <f aca="true">IFERROR(IF($B$7=0,"No sales logged yet for this year.",IF($C$4=YEAR(TODAY()),"Run rate: "&amp;TEXT($B$7/MONTH(TODAY())*12,"$#,##0")&amp;" net per year at the current pace.","Net revenue: "&amp;TEXT($B$7,"$#,##0")&amp;" for "&amp;$C$4&amp;".")),"")</f>
+        <v>Run rate: $69 net per year at the current pace.</v>
+      </c>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
       <c r="K19" s="2"/>
       <c r="L19" s="29" t="str">
         <f aca="false">IF(Products!A13="","",Products!A13)</f>
@@ -8569,12 +8672,12 @@
       </c>
       <c r="N19" s="2"/>
     </row>
-    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="n">
         <v>9</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" s="30" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A20,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A20+1,1))</f>
@@ -8589,27 +8692,30 @@
         <v>0</v>
       </c>
       <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="G20" s="35" t="str">
+        <f aca="false">IFERROR(IF(MAX($C$12:$C$23)=0,"","Best month so far: "&amp;INDEX($B$12:$B$23,MATCH(MAX($C$12:$C$23),$C$12:$C$23,0))&amp;" ("&amp;TEXT(MAX($C$12:$C$23),"$#,##0")&amp;" net)."),"")</f>
+        <v>Best month so far: August ($23 net).</v>
+      </c>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="33" t="str">
+      <c r="L20" s="36" t="str">
         <f aca="false">IF(Products!A14="","",Products!A14)</f>
         <v/>
       </c>
-      <c r="M20" s="34" t="str">
+      <c r="M20" s="37" t="str">
         <f aca="false">IF($L20="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L20,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
       <c r="N20" s="2"/>
     </row>
-    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="n">
         <v>10</v>
       </c>
       <c r="B21" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C21" s="30" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A21,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A21+1,1))</f>
@@ -8624,27 +8730,30 @@
         <v>0</v>
       </c>
       <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="G21" s="35" t="str">
+        <f aca="false">IFERROR(IF(SUMIFS(Income!$D$6:$D$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))=0,"","Platform fees took "&amp;TEXT(SUMIFS(Income!$E$6:$E$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1))/SUMIFS(Income!$D$6:$D$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)),"0.0%")&amp;" of gross this year."),"")</f>
+        <v>Platform fees took 11.6% of gross this year.</v>
+      </c>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="33" t="str">
+      <c r="L21" s="36" t="str">
         <f aca="false">IF(Products!A15="","",Products!A15)</f>
         <v/>
       </c>
-      <c r="M21" s="34" t="str">
+      <c r="M21" s="37" t="str">
         <f aca="false">IF($L21="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L21,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
       <c r="N21" s="2"/>
     </row>
-    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="n">
         <v>11</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C22" s="30" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A22,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A22+1,1))</f>
@@ -8659,16 +8768,19 @@
         <v>0</v>
       </c>
       <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="G22" s="35" t="str">
+        <f aca="false">IFERROR(IF(MAX($M$12:$M$31)=0,"","Bestseller: "&amp;INDEX($L$12:$L$31,MATCH(MAX($M$12:$M$31),$M$12:$M$31,0))&amp;" ("&amp;TEXT(MAX($M$12:$M$31),"$#,##0")&amp;" net)."),"")</f>
+        <v>Bestseller: Invoice Template Pack ($26 net).</v>
+      </c>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
       <c r="K22" s="2"/>
-      <c r="L22" s="33" t="str">
+      <c r="L22" s="36" t="str">
         <f aca="false">IF(Products!A16="","",Products!A16)</f>
         <v/>
       </c>
-      <c r="M22" s="34" t="str">
+      <c r="M22" s="37" t="str">
         <f aca="false">IF($L22="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L22,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -8679,7 +8791,7 @@
         <v>12</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" s="30" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,$A23,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,$A23+1,1))</f>
@@ -8699,11 +8811,11 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-      <c r="L23" s="33" t="str">
+      <c r="L23" s="36" t="str">
         <f aca="false">IF(Products!A17="","",Products!A17)</f>
         <v/>
       </c>
-      <c r="M23" s="34" t="str">
+      <c r="M23" s="37" t="str">
         <f aca="false">IF($L23="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L23,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -8721,11 +8833,11 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="33" t="str">
+      <c r="L24" s="36" t="str">
         <f aca="false">IF(Products!A18="","",Products!A18)</f>
         <v/>
       </c>
-      <c r="M24" s="34" t="str">
+      <c r="M24" s="37" t="str">
         <f aca="false">IF($L24="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L24,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -8734,7 +8846,7 @@
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -8745,11 +8857,11 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="33" t="str">
+      <c r="L25" s="36" t="str">
         <f aca="false">IF(Products!A19="","",Products!A19)</f>
         <v/>
       </c>
-      <c r="M25" s="34" t="str">
+      <c r="M25" s="37" t="str">
         <f aca="false">IF($L25="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L25,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -8760,7 +8872,7 @@
         <v>61</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>63</v>
@@ -8777,11 +8889,11 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-      <c r="L26" s="33" t="str">
+      <c r="L26" s="36" t="str">
         <f aca="false">IF(Products!A20="","",Products!A20)</f>
         <v/>
       </c>
-      <c r="M26" s="34" t="str">
+      <c r="M26" s="37" t="str">
         <f aca="false">IF($L26="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L26,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -8792,7 +8904,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" s="30" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A27-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A27+1,1))</f>
@@ -8812,11 +8924,11 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-      <c r="L27" s="33" t="str">
+      <c r="L27" s="36" t="str">
         <f aca="false">IF(Products!A21="","",Products!A21)</f>
         <v/>
       </c>
-      <c r="M27" s="34" t="str">
+      <c r="M27" s="37" t="str">
         <f aca="false">IF($L27="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L27,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -8827,7 +8939,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C28" s="30" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A28-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A28+1,1))</f>
@@ -8847,11 +8959,11 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-      <c r="L28" s="33" t="str">
+      <c r="L28" s="36" t="str">
         <f aca="false">IF(Products!A22="","",Products!A22)</f>
         <v/>
       </c>
-      <c r="M28" s="34" t="str">
+      <c r="M28" s="37" t="str">
         <f aca="false">IF($L28="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L28,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -8862,7 +8974,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C29" s="30" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A29-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A29+1,1))</f>
@@ -8882,11 +8994,11 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-      <c r="L29" s="33" t="str">
+      <c r="L29" s="36" t="str">
         <f aca="false">IF(Products!A23="","",Products!A23)</f>
         <v/>
       </c>
-      <c r="M29" s="34" t="str">
+      <c r="M29" s="37" t="str">
         <f aca="false">IF($L29="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L29,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -8897,7 +9009,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C30" s="30" t="n">
         <f aca="false">SUMIFS(Income!$F$6:$F$305,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,3*$A30-2,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4,3*$A30+1,1))</f>
@@ -8917,11 +9029,11 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-      <c r="L30" s="33" t="str">
+      <c r="L30" s="36" t="str">
         <f aca="false">IF(Products!A24="","",Products!A24)</f>
         <v/>
       </c>
-      <c r="M30" s="34" t="str">
+      <c r="M30" s="37" t="str">
         <f aca="false">IF($L30="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L30,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -8939,11 +9051,11 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-      <c r="L31" s="33" t="str">
+      <c r="L31" s="36" t="str">
         <f aca="false">IF(Products!A25="","",Products!A25)</f>
         <v/>
       </c>
-      <c r="M31" s="34" t="str">
+      <c r="M31" s="37" t="str">
         <f aca="false">IF($L31="","",SUMIFS(Income!$F$6:$F$305,Income!$B$6:$B$305,$L31,Income!$A$6:$A$305,"&gt;="&amp;DATE($C$4,1,1),Income!$A$6:$A$305,"&lt;"&amp;DATE($C$4+1,1,1)))</f>
         <v/>
       </c>
@@ -9287,7 +9399,7 @@
     </row>
   </sheetData>
   <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false"/>
-  <mergeCells count="10">
+  <mergeCells count="14">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="B6:C6"/>
@@ -9298,6 +9410,10 @@
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="J7:K7"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J22"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
